--- a/Unity/Assets/Config/Excel/MonsterGroupConfig.xlsx
+++ b/Unity/Assets/Config/Excel/MonsterGroupConfig.xlsx
@@ -47,10 +47,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>位置Z</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>PosZ</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -64,6 +60,10 @@
   </si>
   <si>
     <t>int</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>位置z</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -468,10 +468,10 @@
         <v>5</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4" spans="3:7" x14ac:dyDescent="0.3">
@@ -485,10 +485,10 @@
         <v>6</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="3:7" x14ac:dyDescent="0.3">
@@ -505,7 +505,7 @@
         <v>4</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6" spans="3:7" s="1" customFormat="1" x14ac:dyDescent="0.25">

--- a/Unity/Assets/Config/Excel/MonsterGroupConfig.xlsx
+++ b/Unity/Assets/Config/Excel/MonsterGroupConfig.xlsx
@@ -513,35 +513,19 @@
         <v>1</v>
       </c>
       <c r="D6" s="1">
-        <v>141</v>
+        <v>-13</v>
       </c>
       <c r="E6" s="1">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="F6" s="1">
-        <v>237</v>
+        <v>-9</v>
       </c>
       <c r="G6" s="1">
         <v>20</v>
       </c>
     </row>
-    <row r="7" spans="3:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="C7" s="1">
-        <v>2</v>
-      </c>
-      <c r="D7" s="1">
-        <v>160</v>
-      </c>
-      <c r="E7" s="1">
-        <v>0.5</v>
-      </c>
-      <c r="F7" s="1">
-        <v>237</v>
-      </c>
-      <c r="G7" s="1">
-        <v>10</v>
-      </c>
-    </row>
+    <row r="7" spans="3:7" s="1" customFormat="1" x14ac:dyDescent="0.25"/>
     <row r="8" spans="3:7" s="1" customFormat="1" x14ac:dyDescent="0.25"/>
     <row r="9" spans="3:7" s="1" customFormat="1" x14ac:dyDescent="0.25"/>
     <row r="10" spans="3:7" x14ac:dyDescent="0.3">
